--- a/data/daily/2026-10/2026-10-19.xlsx
+++ b/data/daily/2026-10/2026-10-19.xlsx
@@ -1168,7 +1168,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1190,7 +1190,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
@@ -1215,7 +1215,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
@@ -1240,10 +1240,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1265,10 +1265,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1290,7 +1290,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
@@ -1315,10 +1315,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="381000" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1340,7 +1340,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
@@ -1365,7 +1365,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
@@ -1376,31 +1376,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1423,7 +1398,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1443,7 +1418,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1468,7 +1443,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1493,12 +1468,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1518,12 +1493,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1543,7 +1518,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1568,12 +1543,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1593,7 +1568,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1618,7 +1593,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1631,31 +1606,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2084,31 +2034,31 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16304</v>
+        <v>16305</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>피로 회복 및 체력 증진 — 섭취 후 피로가 풀리고 몸이 한결 가벼워지는 느낌을 받음</t>
+          <t>피로 회복 및 활력 증진 — 섭취 후 피로감이 줄어들고 몸이 한결 가벼워지며 힘이 나는 느낌을 받음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 포장이 고급스러워 선물용으로 주고받기에 만족스러움</t>
+          <t>고급스러운 포장과 선물성 — 패키지가 고급스러워 나를 위한 선물이나 타인에게 줄 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>진한 농축 액상 제형 — 액상 원액이 매우 진해 비타민을 효과적으로 섭취하는 느낌이 듦</t>
+          <t>진한 액상 제형 — 비타민 원액이 찐해서 고농축 영양제를 먹는 느낌을 제공함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>아쉬운 배송 속도 — 주문 후 제품 배송이 너무 늦게 도착함</t>
+          <t>느린 배송 속도 — 주문 후 배송 완료까지 시간이 매우 오래 걸림</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>다소 높은 가격대 — 피로 회복 효과는 있으나 다소 비싼 가격이 부담됨</t>
+          <t>부담스러운 가격대 — 제품의 가격이 다소 비싸게 느껴짐</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -2151,21 +2101,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15645</v>
+        <v>15646</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>피로 개선 및 체력 관리 — 피로감을 줄여주고 수면 부족이나 여행 시 챙겨 먹기 적합함</t>
+          <t>간편한 섭취 방식 — 액상 형태로 되어 있어 피로하거나 여행 시 먹기 편함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 섭취 및 맛 — 액상 제형으로 먹기 편하며 맛도 부담 없이 좋음</t>
+          <t>선물용으로 적합한 구성 — 포장이 예쁘고 10입 구성이라 부담 없이 가볍게 체험하거나 선물하기 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>부담 없는 소용량 구성 — 10입 구성으로 대용량을 사기 전 미리 체험해보기 좋음</t>
+          <t>피로 회복 만족도 — 고함량 영양소로 섭취 시 덜 피로하고 건강 관리에 도움을 줌</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2214,17 +2164,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>피로 개선 및 활력 증진 — 섭취 후 피로감이 줄고 하루를 활기차게 시작하는 데 도움을 줌</t>
+          <t>피로 회복 및 생기 부여 — 피로감이 줄어들고 활기찬 하루를 시작하는 데 효과적임</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>넉넉한 대용량 구성 — 30개입 구성으로 넉넉하여 가족과 함께 나눠 먹기 좋음</t>
+          <t>넉넉한 대용량 구성 — 30개입이라 오랫동안 꾸준히 챙겨 먹거나 가족과 나눠 먹기 좋음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>정성스러운 선물 포장 — 예쁜 포장 디자인으로 선물 받는 사람의 만족도가 높음</t>
+          <t>감동적인 선물 패키지 — 포장이 정성스럽고 예뻐서 받는 사람의 만족도가 높음</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2273,22 +2223,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 물 없이 씹어 먹는 과일맛 젤리라 거부감 없이 간식처럼 먹기 좋음</t>
+          <t>맛있는 젤리 형태 — 과일맛 젤리 제형이라 거부감 없이 간식처럼 맛있게 섭취함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>안전 용기 캡 적용 — 안전캡이 내장되어 아이가 있는 집에서도 안심하고 보관 가능함</t>
+          <t>물 없는 간편한 섭취 — 바쁜 아침이나 출근길에도 물 없이 씹어서 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>우수한 복용 편의성 — 바쁜 아침에도 시간 절약하며 간편하게 영양을 챙길 수 있음</t>
+          <t>안전캡 용기 적용 — 안전캡이 있어 아이가 있는 집에서도 안심하고 보관함</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>맛으로 인한 섭취 제한 — 맛이 너무 좋아 하루 권장량 이상으로 계속 먹게 됨</t>
+          <t>일일 섭취량 제한 — 맛이 좋아 계속 먹고 싶지만 하루 정량만 먹어야 해서 아쉬움</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2336,18 +2286,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 며칠간 섭취 시 혓바늘 완화 등 피로 회복 체감이 뛰어남</t>
+          <t>빠른 컨디션 회복 효과 — 피로 해소에 탁월하며 혓바늘 등 구내 염증 완화에 빠른 효과를 보임</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>할인 행사로 가성비 확보 — 세일이나 이벤트를 통해 저렴한 가격에 합리적으로 구매 가능함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>할인 프로모션가 — 세일 및 추가 증정 이벤트를 통해 가성비 좋게 구매함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>올인원 영양 보충 — 한 포에 액상과 정제가 함께 들어 있어 한 번에 다양한 영양소를 챙김</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>짧은 유통기한 아쉬움 — 남은 유통기한이 생각보다 짧아 빠르게 소비해야 함</t>
+          <t>짧은 유통기한 — 할인 특가 구매 시 소비기한 및 유통기한이 다소 짧은 편임</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2391,19 +2345,23 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>피로 회복 및 컨디션 유지 — 피로를 잘 풀어주고 환절기 몸 상태 관리에 도움을 줌</t>
+          <t>피로 해소 및 컨디션 관리 — 환절기 건강 관리와 일상 속 피로 회복에 효과적임</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>우수한 휴대성과 편의성 — 먹기 편하고 가방에 간편하게 들고 다니기 좋음</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>우수한 휴대성과 섭취 편의 — 가지고 다니기 편리하고 먹기 쉬운 형태임</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>만족스러운 구성과 배송 — 제품 구성이 알차고 배송이 빠르며 선물용으로 적합함</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2446,29 +2404,33 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>신개념 믹스 섭취 방식 — 버튼을 누르면 분말과 액상이 섞여 색이 변하는 재미가 있음</t>
+          <t>체력 및 에너지 충전 — 지친 일상이나 피로감이 심할 때 섭취하면 생기와 에너지가 생김</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>피로 회복 및 에너지 충전 — 마신 후 피로가 풀리고 몸에 생기가 도는 것을 느낌</t>
+          <t>재미있는 용기 메커니즘 — 버튼을 누르면 분말이 노랗게 섞여 색이 변하는 재미가 있음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 패키지 포장이 예쁘고 고급스러워 주변 선물용으로 우수함</t>
+          <t>고급스러운 포장 디자인 — 포장이 고급스럽고 세련되어 선물용 만족도가 매우 높음</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>쌉쌀한 맛과 사용법 안내 — 분말이 섞이면 다소 쌉쌀하며 사전 사용법 안내가 필요함</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>섭취 방법 안내 필요 — 분말을 섞지 않고 겉의 투명한 액상만 마실 위험이 있어 사전 설명이 필요함</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>분말의 쌉싸름한 맛 — 가루가 섞이면서 약 특유의 쌉싸름한 맛이 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
@@ -2513,18 +2475,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>면역력 및 건강 관리 — 감기 초기나 입병 예방 및 피부 건강 케어에 체감 효과가 있음</t>
+          <t>면역력 강화 및 증상 완화 — 감기 초기나 입병 예방에 효과가 있으며 피부 상태 개선을 체감함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>할인가로 가성비 확보 — 할인 혜택 기간에 저렴한 가격으로 구매할 수 있음</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>빠른 배송 및 저렴한 가격 — 배송이 빠르고 카쇼페 할인가 등을 통해 착한 가격으로 구매함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>넉넉한 용량 구성 — 100포의 대용량으로 온 가족이 구비해 두고 먹기 좋음</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>강한 신맛과 쓴맛 — 분말 특유의 신맛과 쓴맛이 매우 강력해 호불호가 갈림</t>
+          <t>강한 신맛과 쓴맛 — 분말 특유의 신맛과 쓴맛이 강해 먹기 힘들 수 있음</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -2533,7 +2499,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2541,46 +2507,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>온가족 유산균 선물 ALL NEW 락토핏 골드 3통 + 아임비타 이뮨샷 4병 추가증정</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32,700원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/682864</t>
+          <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261018111100_823e5a0bdcf24c7e938d9ca85b824be9.jpeg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>534</v>
+        <v>8756</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 구성 — 할인가 구매가 가능하고 유용한 사은품까지 함께 제공됨</t>
+          <t>마시는 액상 제형 — 액상 형태로 되어 있어 간편하게 마실 수 있음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>신속한 배송 서비스 — 주문 후 빠르게 제품을 수령할 수 있음</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>다음 날 느껴지는 효과 — 섭취 후 숙면을 취하면 다음 날 컨디션이 좋아지고 에너지가 생김</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>센스 있는 선물용 — 지인이나 어른들 생일 선물용으로 인기가 많음</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -2596,46 +2566,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10056171</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261006173014_9a46de80b829480796c23d0cd4a75de9.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>8755</v>
+        <v>839</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>즉각적인 컨디션 개선 — 섭취 후 수면을 취하면 다음 날 몸 상태가 확연히 개운해짐</t>
+          <t>확실한 피로 해소 — 한 병 마시면 하루 종일 힘이 나고 피로가 싹 사라짐</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성과 간편성 — 한 포씩 가방에 넣어 가지고 다니며 간편히 마실 수 있음</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>위생적인 이중 구조 — 액상과 정제가 구분되어 있어 깔끔하고 위생적으로 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>뛰어난 휴대성 — 외출이나 야외 활동 시 들고 다니며 챙겨 먹기 편함</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -2682,22 +2656,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>소화 촉진 및 속 편함 — 더부룩함이나 체기가 있을 때 먹으면 소화가 잘되고 배변을 도움</t>
+          <t>소화 및 속 편안함 — 더부룩함이나 체기가 가라앉고 화장실을 잘 가도록 도와줌</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>고소하고 부담 없는 맛 — 맛이 고소하여 아이부터 성인까지 거부감 없이 복용 가능함</t>
+          <t>고소하고 우수한 맛 — 맛이 고소하여 아이들도 거부감 없이 맛있게 먹음</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>알찬 추가 사은품 증정 — 견과류바 등 다채로운 증정품이 함께 와 만족도가 높음</t>
+          <t>푸짐한 할인과 증정품 — 핫딜 구매 시 가격이 저렴하고 견과류바 등 추가 증정품 구성이 알참</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>이벤트 경품 안내 미흡 — 추가 증정 기프티콘 발송 방식이나 대상 안내가 다소 불명확함</t>
+          <t>기프티콘 발송 안내 누락 — 추첨 증정 기프티콘의 발송 대상이나 수령 방법 안내가 불명확함</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -2745,23 +2719,23 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>소화 촉진 및 장 건강 개선 — 식후 섭취 시 배에 가스가 차지 않고 숙변 배출 및 소화를 돕음</t>
+          <t>소화 및 숙변 제거 효과 — 식후 소화가 잘 되고 뱃속 가스 완화 및 숙변 배출에 도움됨</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>풍성한 사은품 혜택 — 저렴한 가격에 유용한 사은품이 많이 제공됨</t>
+          <t>풍성한 사은품 구성 — 할인된 가격과 더불어 푸짐한 사은품을 함께 제공함</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>거부감 드는 맛과 향 — 기존 시리즈에 비해 특유의 냄새와 맛이 아쉬움을 줌</t>
+          <t>아쉬운 맛과 냄새 — 기존 프리미엄 라인 대비 냄새와 맛이 아쉽게 느껴짐</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>교환 및 환불 제약 — 구매 후 교환이나 환불이 불가능하다는 조건이 아쉬움</t>
+          <t>교환 및 환불 불가 정책 — 구매 후 교환이나 환불 처리가 되지 않는 점이 불만족스러움</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -2808,28 +2782,28 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>높은 포만감과 맛 — 소스 맛이 뛰어나고 한 개만 먹어도 포만감이 오래 유지됨</t>
+          <t>풍부한 맛과 포만감 — 맛이 뛰어나며 한 개만 먹어도 포만감이 오래 지속됨</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>다양한 맛 패키지 — 다채로운 양념 맛으로 질리지 않게 다이어트 식단을 챙김</t>
+          <t>알찬 식단 구성과 가성비 — 할인가 구매 시 구성이 다양하고 보냉백 사은품 디자인이 예쁨</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>다소 강한 양념 간 — 일부 제품의 간이 센 편이라 밥과 함께 먹어야 적당함</t>
+          <t>다소 강한 간 — 단독 섭취 시 생각보다 간이 세게 느껴져 밥과 함께 먹어야 함</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>오배송 및 문의 응대 미흡 — 구성품이 잘못 배송되거나 문의 연락이 닿지 않음</t>
+          <t>오배송 및 문의 미응답 — 제품 옵션이 잘못 중복 배송되었으나 판매자 응답이 없음</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>배송 중 포장 터짐 발생 — 포장이 헐렁하거나 팩이 터져 소스가 묻어나오는 경우가 있음</t>
+          <t>포장 터짐 및 진공 불량 — 배송 중 일부 밀봉 포장이 터지거나 진공이 풀어져서 도착함</t>
         </is>
       </c>
     </row>
@@ -2875,15 +2849,19 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>맛있는 효소 맛 — 맛이 좋아 거부감 없이 간식용으로 즐기기에 적합함</t>
+          <t>맛있는 간식 대용 — 효소 맛이 좋아 출출할 때 간식처럼 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>고퀄리티 사은품 구성 — 맛있는 단백질바와 예쁜 디자인의 포토카드가 증정됨</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>고퀄리티 사은품 증정 — 함께 증정되는 포토카드와 단백질바의 만족도가 매우 높음</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>깔끔한 디자인과 포장 — 패키지 포장이 깔끔하고 제품 디자인과 사이즈가 우수함</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -2930,17 +2908,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 퍽퍽하지 않고 촉촉하며 소스가 맛있어 질리지 않음</t>
+          <t>촉촉한 식감과 뛰어난 맛 — 퍽퍽하지 않고 촉촉해서 맛있는 닭가슴살임</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>간편한 전자레인지 조리 — 전자레인지에 바로 데워 먹을 수 있어 준비가 간단함</t>
+          <t>질리지 않는 다양한 맛 — 떡볶이맛 등 다채로운 소스가 함유되어 식단 관리에 용이함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>질리지 않는 다채로운 구성 — 여러 다양한 맛으로 식단 관리를 지속하기 좋음</t>
+          <t>간편한 조리 및 합리적 가격 — 전자레인지 조리로 간편하며 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2989,18 +2967,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>고급스러운 에디션 포장 — 포장과 세트 구성품이 고급스러워 선물용으로 완벽함</t>
+          <t>고급스럽고 예쁜 패키지 — 플리츠백과 정성스러운 포장 구성으로 받는 사람의 기분이 좋아짐</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>비린 맛 없는 달콤한 맛 — 비린 느낌이 없고 맛있어 일상에서 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>맛있는 앰플 제형 — 비린 맛 없이 맛있어서 매일 챙겨 마시기 편함</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>피로 완화 효과 — 섭취 후 덜 피곤하고 피부 탄력 개선에 도움이 됨</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>다소 부담스러운 가격 — 가격대가 다소 높아 할인 행사 시 구매하게 됨</t>
+          <t>높은 가격대 — 제품의 정상 가격이 비싸서 할인 행사 때만 구매하게 됨</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3044,21 +3026,21 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>탁월한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 두통 없이 개운한 상태를 유지함</t>
+          <t>확실한 숙취 및 두통 해소 — 음주 전후 섭취 시 다음 날 머리 아픔과 숙취가 현저히 줄어듦</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>우수한 휴대성과 편의성 — 스틱형 포장으로 가방에 넣어 다니며 간편히 먹기 좋음</t>
+          <t>휴대성 좋은 개별 포장 — 스틱형으로 가방에 챙겨 다니며 필요할 때 먹기 편함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>선물용으로 적합한 포장 — 패키지 및 선물용 가방 구성이 고급스러워 선물하기 적합함</t>
+          <t>모임 선물용으로 적합 — 박스 및 세트 포장이 튼튼하고 고급스러워 주변 나누어 주기 좋음</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3107,22 +3089,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>속 편한 락토프리 공법 — 락토프리 제품으로 속 더부룩함 없이 편안하게 마심</t>
+          <t>비린 맛 없는 음료 풍미 — 단백질 특유의 텁텁함이나 비린 맛 없이 일반 바나나 우유처럼 맛있음</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔한 맛 — 단백질 특유의 비린 맛이 없고 달콤하여 음료처럼 마시기 좋음</t>
+          <t>속 편한 락토프리 — 락토프리 제품이라 마신 후 속이 편안함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>알찬 추가 사은품 증정 — 에너지바 등 단백질바 사은품이 함께 제공됨</t>
+          <t>아침 식사 대용 — 아침이나 운동 전후로 간편하게 단백질을 충전함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>호불호 갈리는 특정 맛 — 밀크바나나 등 일부 맛의 경우 다소 느끼하게 느껴질 수 있음</t>
+          <t>특정 맛의 느끼함 — 밀크바나나 등 일부 맛의 경우 다소 느끼하게 느껴질 수 있음</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -3139,48 +3121,48 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
+          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>크런틴</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>58,200원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14408269</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261014163835_db2fb775478047e286699c91aca83ed4.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>풍부한 토핑과 바삭한 식감 — 크런치볼 토핑이 듬뿍 들어있어 씹는 식감이 좋고 달콤함</t>
+          <t>달콤하고 맛있는 풍미 — 비린 맛 없이 일반 모카라떼나 초코우유처럼 달콤하고 맛있음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>오래 유지되는 포만감 — 섭취 후 든든함이 오래 지속되어 식사 대용으로 훌륭함</t>
+          <t>은근한 포만감 — 마시고 나면 은근히 배가 차서 입이 심심할 때 간식용으로 좋음</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>간편한 파우치형 구조 — 물이나 우유만 부어 흔들어 마시고 간편히 버릴 수 있음</t>
+          <t>운동 후 단백질 섭취 — 운동 후 깔끔하게 한 팩씩 마시며 관리하기 적합함</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3198,46 +3180,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
+          <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>크런틴</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>58,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/14408269</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261019115059_ac5fb17ea3454c8a91aacd4c95250543.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>218</v>
+        <v>10</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>음료 같은 달콤한 맛 — 단백질 특유의 비린 맛이 없고 진한 초코우유나 음료처럼 맛있음</t>
+          <t>바삭한 토핑과 식감 — 크런치볼과 토핑이 듬뿍 들어있어 씹는 재미가 있고 든든함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>적절한 포만감 제공 — 음용 후 배가 쉽게 고프지 않아 운동 후나 간식으로 적합함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>물만 넣어도 뛰어난 맛 — 맹물만 넣어 흔들어 먹어도 텁텁함 없이 시리얼이나 매장 음료처럼 맛있음</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>휴대성 높은 파우치 형태 — 파우치 형태로 되어 있어 타 먹고 버리기 편리함</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -3393,7 +3379,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -3450,12 +3436,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>닥터블릿</t>
         </is>
       </c>
     </row>
@@ -3507,12 +3493,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>온가족 유산균 선물 ALL NEW 락토핏 골드 3통 + 아임비타 이뮨샷 4병 추가증정</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병</t>
         </is>
       </c>
     </row>
@@ -3560,10 +3546,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16304</v>
+        <v>16305</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15645</v>
+        <v>15646</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3414</v>
@@ -3575,19 +3561,19 @@
         <v>129</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>969</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>534</v>
+        <v>8756</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>8755</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -3598,67 +3584,72 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 체력 증진 — 섭취 후 피로가 풀리고 몸이 한결 가벼워지는 느낌을 받음
-고급스러운 선물용 포장 — 포장이 고급스러워 선물용으로 주고받기에 만족스러움
-진한 농축 액상 제형 — 액상 원액이 매우 진해 비타민을 효과적으로 섭취하는 느낌이 듦</t>
+          <t>피로 회복 및 활력 증진 — 섭취 후 피로감이 줄어들고 몸이 한결 가벼워지며 힘이 나는 느낌을 받음
+고급스러운 포장과 선물성 — 패키지가 고급스러워 나를 위한 선물이나 타인에게 줄 선물용으로 적합함
+진한 액상 제형 — 비타민 원액이 찐해서 고농축 영양제를 먹는 느낌을 제공함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>피로 개선 및 체력 관리 — 피로감을 줄여주고 수면 부족이나 여행 시 챙겨 먹기 적합함
-간편한 섭취 및 맛 — 액상 제형으로 먹기 편하며 맛도 부담 없이 좋음
-부담 없는 소용량 구성 — 10입 구성으로 대용량을 사기 전 미리 체험해보기 좋음</t>
+          <t>간편한 섭취 방식 — 액상 형태로 되어 있어 피로하거나 여행 시 먹기 편함
+선물용으로 적합한 구성 — 포장이 예쁘고 10입 구성이라 부담 없이 가볍게 체험하거나 선물하기 좋음
+피로 회복 만족도 — 고함량 영양소로 섭취 시 덜 피로하고 건강 관리에 도움을 줌</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>피로 개선 및 활력 증진 — 섭취 후 피로감이 줄고 하루를 활기차게 시작하는 데 도움을 줌
-넉넉한 대용량 구성 — 30개입 구성으로 넉넉하여 가족과 함께 나눠 먹기 좋음
-정성스러운 선물 포장 — 예쁜 포장 디자인으로 선물 받는 사람의 만족도가 높음</t>
+          <t>피로 회복 및 생기 부여 — 피로감이 줄어들고 활기찬 하루를 시작하는 데 효과적임
+넉넉한 대용량 구성 — 30개입이라 오랫동안 꾸준히 챙겨 먹거나 가족과 나눠 먹기 좋음
+감동적인 선물 패키지 — 포장이 정성스럽고 예뻐서 받는 사람의 만족도가 높음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 물 없이 씹어 먹는 과일맛 젤리라 거부감 없이 간식처럼 먹기 좋음
-안전 용기 캡 적용 — 안전캡이 내장되어 아이가 있는 집에서도 안심하고 보관 가능함
-우수한 복용 편의성 — 바쁜 아침에도 시간 절약하며 간편하게 영양을 챙길 수 있음</t>
+          <t>맛있는 젤리 형태 — 과일맛 젤리 제형이라 거부감 없이 간식처럼 맛있게 섭취함
+물 없는 간편한 섭취 — 바쁜 아침이나 출근길에도 물 없이 씹어서 챙겨 먹기 편함
+안전캡 용기 적용 — 안전캡이 있어 아이가 있는 집에서도 안심하고 보관함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 며칠간 섭취 시 혓바늘 완화 등 피로 회복 체감이 뛰어남
-할인 행사로 가성비 확보 — 세일이나 이벤트를 통해 저렴한 가격에 합리적으로 구매 가능함</t>
+          <t>빠른 컨디션 회복 효과 — 피로 해소에 탁월하며 혓바늘 등 구내 염증 완화에 빠른 효과를 보임
+할인 프로모션가 — 세일 및 추가 증정 이벤트를 통해 가성비 좋게 구매함
+올인원 영양 보충 — 한 포에 액상과 정제가 함께 들어 있어 한 번에 다양한 영양소를 챙김</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 컨디션 유지 — 피로를 잘 풀어주고 환절기 몸 상태 관리에 도움을 줌
-우수한 휴대성과 편의성 — 먹기 편하고 가방에 간편하게 들고 다니기 좋음</t>
+          <t>피로 해소 및 컨디션 관리 — 환절기 건강 관리와 일상 속 피로 회복에 효과적임
+우수한 휴대성과 섭취 편의 — 가지고 다니기 편리하고 먹기 쉬운 형태임
+만족스러운 구성과 배송 — 제품 구성이 알차고 배송이 빠르며 선물용으로 적합함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>신개념 믹스 섭취 방식 — 버튼을 누르면 분말과 액상이 섞여 색이 변하는 재미가 있음
-피로 회복 및 에너지 충전 — 마신 후 피로가 풀리고 몸에 생기가 도는 것을 느낌
-고급스러운 선물 포장 — 패키지 포장이 예쁘고 고급스러워 주변 선물용으로 우수함</t>
+          <t>체력 및 에너지 충전 — 지친 일상이나 피로감이 심할 때 섭취하면 생기와 에너지가 생김
+재미있는 용기 메커니즘 — 버튼을 누르면 분말이 노랗게 섞여 색이 변하는 재미가 있음
+고급스러운 포장 디자인 — 포장이 고급스럽고 세련되어 선물용 만족도가 매우 높음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>면역력 및 건강 관리 — 감기 초기나 입병 예방 및 피부 건강 케어에 체감 효과가 있음
-할인가로 가성비 확보 — 할인 혜택 기간에 저렴한 가격으로 구매할 수 있음</t>
+          <t>면역력 강화 및 증상 완화 — 감기 초기나 입병 예방에 효과가 있으며 피부 상태 개선을 체감함
+빠른 배송 및 저렴한 가격 — 배송이 빠르고 카쇼페 할인가 등을 통해 착한 가격으로 구매함
+넉넉한 용량 구성 — 100포의 대용량으로 온 가족이 구비해 두고 먹기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 구성 — 할인가 구매가 가능하고 유용한 사은품까지 함께 제공됨
-신속한 배송 서비스 — 주문 후 빠르게 제품을 수령할 수 있음</t>
+          <t>마시는 액상 제형 — 액상 형태로 되어 있어 간편하게 마실 수 있음
+다음 날 느껴지는 효과 — 섭취 후 숙면을 취하면 다음 날 컨디션이 좋아지고 에너지가 생김
+센스 있는 선물용 — 지인이나 어른들 생일 선물용으로 인기가 많음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>즉각적인 컨디션 개선 — 섭취 후 수면을 취하면 다음 날 몸 상태가 확연히 개운해짐
-뛰어난 휴대성과 간편성 — 한 포씩 가방에 넣어 가지고 다니며 간편히 마실 수 있음</t>
+          <t>확실한 피로 해소 — 한 병 마시면 하루 종일 힘이 나고 피로가 싹 사라짐
+위생적인 이중 구조 — 액상과 정제가 구분되어 있어 깔끔하고 위생적으로 먹을 수 있음
+뛰어난 휴대성 — 외출이나 야외 활동 시 들고 다니며 챙겨 먹기 편함</t>
         </is>
       </c>
     </row>
@@ -3670,31 +3661,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 배송 속도 — 주문 후 제품 배송이 너무 늦게 도착함
-다소 높은 가격대 — 피로 회복 효과는 있으나 다소 비싼 가격이 부담됨</t>
+          <t>느린 배송 속도 — 주문 후 배송 완료까지 시간이 매우 오래 걸림
+부담스러운 가격대 — 제품의 가격이 다소 비싸게 느껴짐</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>맛으로 인한 섭취 제한 — 맛이 너무 좋아 하루 권장량 이상으로 계속 먹게 됨</t>
+          <t>일일 섭취량 제한 — 맛이 좋아 계속 먹고 싶지만 하루 정량만 먹어야 해서 아쉬움</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>짧은 유통기한 아쉬움 — 남은 유통기한이 생각보다 짧아 빠르게 소비해야 함</t>
+          <t>짧은 유통기한 — 할인 특가 구매 시 소비기한 및 유통기한이 다소 짧은 편임</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>쌉쌀한 맛과 사용법 안내 — 분말이 섞이면 다소 쌉쌀하며 사전 사용법 안내가 필요함</t>
+          <t>섭취 방법 안내 필요 — 분말을 섞지 않고 겉의 투명한 액상만 마실 위험이 있어 사전 설명이 필요함
+분말의 쌉싸름한 맛 — 가루가 섞이면서 약 특유의 쌉싸름한 맛이 느껴질 수 있음</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>강한 신맛과 쓴맛 — 분말 특유의 신맛과 쓴맛이 매우 강력해 호불호가 갈림</t>
+          <t>강한 신맛과 쓴맛 — 분말 특유의 신맛과 쓴맛이 강해 먹기 힘들 수 있음</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
@@ -3748,12 +3740,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>32,700원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>52,900원</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3985,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
           <t>크런틴</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4042,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
         </is>
       </c>
     </row>
@@ -4121,16 +4113,16 @@
         <v>757</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>30</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>10</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>218</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4141,67 +4133,70 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>소화 촉진 및 속 편함 — 더부룩함이나 체기가 있을 때 먹으면 소화가 잘되고 배변을 도움
-고소하고 부담 없는 맛 — 맛이 고소하여 아이부터 성인까지 거부감 없이 복용 가능함
-알찬 추가 사은품 증정 — 견과류바 등 다채로운 증정품이 함께 와 만족도가 높음</t>
+          <t>소화 및 속 편안함 — 더부룩함이나 체기가 가라앉고 화장실을 잘 가도록 도와줌
+고소하고 우수한 맛 — 맛이 고소하여 아이들도 거부감 없이 맛있게 먹음
+푸짐한 할인과 증정품 — 핫딜 구매 시 가격이 저렴하고 견과류바 등 추가 증정품 구성이 알참</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>소화 촉진 및 장 건강 개선 — 식후 섭취 시 배에 가스가 차지 않고 숙변 배출 및 소화를 돕음
-풍성한 사은품 혜택 — 저렴한 가격에 유용한 사은품이 많이 제공됨</t>
+          <t>소화 및 숙변 제거 효과 — 식후 소화가 잘 되고 뱃속 가스 완화 및 숙변 배출에 도움됨
+풍성한 사은품 구성 — 할인된 가격과 더불어 푸짐한 사은품을 함께 제공함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>높은 포만감과 맛 — 소스 맛이 뛰어나고 한 개만 먹어도 포만감이 오래 유지됨
-다양한 맛 패키지 — 다채로운 양념 맛으로 질리지 않게 다이어트 식단을 챙김</t>
+          <t>풍부한 맛과 포만감 — 맛이 뛰어나며 한 개만 먹어도 포만감이 오래 지속됨
+알찬 식단 구성과 가성비 — 할인가 구매 시 구성이 다양하고 보냉백 사은품 디자인이 예쁨</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 효소 맛 — 맛이 좋아 거부감 없이 간식용으로 즐기기에 적합함
-고퀄리티 사은품 구성 — 맛있는 단백질바와 예쁜 디자인의 포토카드가 증정됨</t>
+          <t>맛있는 간식 대용 — 효소 맛이 좋아 출출할 때 간식처럼 맛있게 먹을 수 있음
+고퀄리티 사은품 증정 — 함께 증정되는 포토카드와 단백질바의 만족도가 매우 높음
+깔끔한 디자인과 포장 — 패키지 포장이 깔끔하고 제품 디자인과 사이즈가 우수함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 퍽퍽하지 않고 촉촉하며 소스가 맛있어 질리지 않음
-간편한 전자레인지 조리 — 전자레인지에 바로 데워 먹을 수 있어 준비가 간단함
-질리지 않는 다채로운 구성 — 여러 다양한 맛으로 식단 관리를 지속하기 좋음</t>
+          <t>촉촉한 식감과 뛰어난 맛 — 퍽퍽하지 않고 촉촉해서 맛있는 닭가슴살임
+질리지 않는 다양한 맛 — 떡볶이맛 등 다채로운 소스가 함유되어 식단 관리에 용이함
+간편한 조리 및 합리적 가격 — 전자레인지 조리로 간편하며 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 에디션 포장 — 포장과 세트 구성품이 고급스러워 선물용으로 완벽함
-비린 맛 없는 달콤한 맛 — 비린 느낌이 없고 맛있어 일상에서 챙겨 먹기 좋음</t>
+          <t>고급스럽고 예쁜 패키지 — 플리츠백과 정성스러운 포장 구성으로 받는 사람의 기분이 좋아짐
+맛있는 앰플 제형 — 비린 맛 없이 맛있어서 매일 챙겨 마시기 편함
+피로 완화 효과 — 섭취 후 덜 피곤하고 피부 탄력 개선에 도움이 됨</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>탁월한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 두통 없이 개운한 상태를 유지함
-우수한 휴대성과 편의성 — 스틱형 포장으로 가방에 넣어 다니며 간편히 먹기 좋음
-선물용으로 적합한 포장 — 패키지 및 선물용 가방 구성이 고급스러워 선물하기 적합함</t>
+          <t>확실한 숙취 및 두통 해소 — 음주 전후 섭취 시 다음 날 머리 아픔과 숙취가 현저히 줄어듦
+휴대성 좋은 개별 포장 — 스틱형으로 가방에 챙겨 다니며 필요할 때 먹기 편함
+모임 선물용으로 적합 — 박스 및 세트 포장이 튼튼하고 고급스러워 주변 나누어 주기 좋음</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 락토프리 공법 — 락토프리 제품으로 속 더부룩함 없이 편안하게 마심
-비린 맛 없는 깔끔한 맛 — 단백질 특유의 비린 맛이 없고 달콤하여 음료처럼 마시기 좋음
-알찬 추가 사은품 증정 — 에너지바 등 단백질바 사은품이 함께 제공됨</t>
+          <t>비린 맛 없는 음료 풍미 — 단백질 특유의 텁텁함이나 비린 맛 없이 일반 바나나 우유처럼 맛있음
+속 편한 락토프리 — 락토프리 제품이라 마신 후 속이 편안함
+아침 식사 대용 — 아침이나 운동 전후로 간편하게 단백질을 충전함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>풍부한 토핑과 바삭한 식감 — 크런치볼 토핑이 듬뿍 들어있어 씹는 식감이 좋고 달콤함
-오래 유지되는 포만감 — 섭취 후 든든함이 오래 지속되어 식사 대용으로 훌륭함
-간편한 파우치형 구조 — 물이나 우유만 부어 흔들어 마시고 간편히 버릴 수 있음</t>
+          <t>달콤하고 맛있는 풍미 — 비린 맛 없이 일반 모카라떼나 초코우유처럼 달콤하고 맛있음
+은근한 포만감 — 마시고 나면 은근히 배가 차서 입이 심심할 때 간식용으로 좋음
+운동 후 단백질 섭취 — 운동 후 깔끔하게 한 팩씩 마시며 관리하기 적합함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>음료 같은 달콤한 맛 — 단백질 특유의 비린 맛이 없고 진한 초코우유나 음료처럼 맛있음
-적절한 포만감 제공 — 음용 후 배가 쉽게 고프지 않아 운동 후나 간식으로 적합함</t>
+          <t>바삭한 토핑과 식감 — 크런치볼과 토핑이 듬뿍 들어있어 씹는 재미가 있고 든든함
+물만 넣어도 뛰어난 맛 — 맹물만 넣어 흔들어 먹어도 텁텁함 없이 시리얼이나 매장 음료처럼 맛있음
+휴대성 높은 파우치 형태 — 파우치 형태로 되어 있어 타 먹고 버리기 편리함</t>
         </is>
       </c>
     </row>
@@ -4213,33 +4208,33 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>이벤트 경품 안내 미흡 — 추가 증정 기프티콘 발송 방식이나 대상 안내가 다소 불명확함</t>
+          <t>기프티콘 발송 안내 누락 — 추첨 증정 기프티콘의 발송 대상이나 수령 방법 안내가 불명확함</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>거부감 드는 맛과 향 — 기존 시리즈에 비해 특유의 냄새와 맛이 아쉬움을 줌
-교환 및 환불 제약 — 구매 후 교환이나 환불이 불가능하다는 조건이 아쉬움</t>
+          <t>아쉬운 맛과 냄새 — 기존 프리미엄 라인 대비 냄새와 맛이 아쉽게 느껴짐
+교환 및 환불 불가 정책 — 구매 후 교환이나 환불 처리가 되지 않는 점이 불만족스러움</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>다소 강한 양념 간 — 일부 제품의 간이 센 편이라 밥과 함께 먹어야 적당함
-오배송 및 문의 응대 미흡 — 구성품이 잘못 배송되거나 문의 연락이 닿지 않음
-배송 중 포장 터짐 발생 — 포장이 헐렁하거나 팩이 터져 소스가 묻어나오는 경우가 있음</t>
+          <t>다소 강한 간 — 단독 섭취 시 생각보다 간이 세게 느껴져 밥과 함께 먹어야 함
+오배송 및 문의 미응답 — 제품 옵션이 잘못 중복 배송되었으나 판매자 응답이 없음
+포장 터짐 및 진공 불량 — 배송 중 일부 밀봉 포장이 터지거나 진공이 풀어져서 도착함</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>다소 부담스러운 가격 — 가격대가 다소 높아 할인 행사 시 구매하게 됨</t>
+          <t>높은 가격대 — 제품의 정상 가격이 비싸서 할인 행사 때만 구매하게 됨</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 특정 맛 — 밀크바나나 등 일부 맛의 경우 다소 느끼하게 느껴질 수 있음</t>
+          <t>특정 맛의 느끼함 — 밀크바나나 등 일부 맛의 경우 다소 느끼하게 느껴질 수 있음</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
@@ -4293,12 +4288,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>28,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>58,200원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>28,900원</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4483,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4496,58 +4491,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2888</v>
+        <v>864</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 도움 — 섭취 후 화장실을 쉽게 갈 수 있도록 도움을 줌</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>초저가 가성비 — 천원이라는 저렴한 가격으로 부담 없이 다이어트 및 건강 관리 가능함</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>붓기 및 식곤증 완화 — 얼굴 붓기가 덜해지고 식후 졸음 현상이 줄어드는 느낌을 받음</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>졸음 및 피로감 유발 — 섭취 후 졸음이 심하게 오거나 피로감이 느껴지는 현상이 있음</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>미미한 체감 효과 — 체중 감량이나 신체 변화 등의 효과가 명확히 느껴지지 않음</t>
-        </is>
-      </c>
+          <t>체감 효과 미비 — 눈에 띄는 다이어트 체감 효과는 명확하지 않음</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4555,62 +4550,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
+          <t>대웅제약 셀레늄 아연 30정 30일분</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
-        </is>
-      </c>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000313&amp;recmYn=N</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2925</v>
+        <v>27</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>익숙한 일반 커피 맛 — 일반 커피와 유사한 맛으로 부담 없이 즐기기 좋음</t>
+          <t>재구매 만족도 — 복용 후 개인적으로 효과를 보아 계속 쟁여두고 먹음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 저렴한 가격으로 부담 없이 사서 챙겨 먹기 유용함</t>
+          <t>간편한 영양 보충 — 필요한 아연과 셀레늄을 손쉽게 보충할 수 있음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>은은한 한방 향 감돌음 — 커피 맛 뒤에 약간의 한방 향이 느껴져 호불호가 갈림</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>적은 분량의 용량 — 한 상자에 5일분만 들어있어 금방 소진되는 점이 아쉬움</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4618,58 +4597,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260930/WeHdQCGpAxVMhBizdMLr030086178_00_00WeHdQCGpAxVMhBizdMLr.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>994</v>
+        <v>843</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>편리한 가루포 제형 — 사탕보다 먹기 편한 분말 형태라 간편하게 한 포씩 챙기기 좋음</t>
+          <t>운동 후 건강 관리 — 운동 후 섭취 시 체감 효과가 좋음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 — 가격이 저렴하여 부담 없이 영양을 보충하기 좋음</t>
+          <t>제품 만족도 — 사용 후 만족스러워 재구매하여 꾸준히 복용함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>강한 단맛과 사탕 느낌 — 단맛이 강해 비타민 영양제보다는 레몬사탕에 가깝게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4677,43 +4652,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 6정 6일분</t>
+          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000280&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602124&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/1DUhwiP05cMCEONDxu7B600000280_00_011DUhwiP05cMCEONDxu7B.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251216/mSQXyRQCV8ORV8edPm4n613602124_00_01mSQXyRQCV8ORV8edPm4n.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>1952</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>부담 없는 착한 가격 — 다이소 특유의 저렴한 가격으로 밀크씨슬을 챙길 수 있음</t>
+          <t>저렴한 구매 가격 — 비싼 멀티비타민을 다이소에서 저렴하게 구매할 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 휴대성 — 6정 소포장이라 여행이나 외출 시 간편히 지니기 좋음</t>
+          <t>피로할 때 빠른 충전 — 피곤할 때 먹기 좋으며 맛도 무난함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -4732,12 +4707,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] [인교진 PICK] 60+ 에너지 올인원 12포 12일분</t>
+          <t>홀베리 유기농 레몬생강즙 10포</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4747,37 +4722,41 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991015&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923424&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260928/l1oJEpcMW3zJ6WbPQVx3033991015_00_00l1oJEpcMW3zJ6WbPQVx3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260904/TyBV46Gp3x0VYWqJvrvs965923424_00_00TyBV46Gp3x0VYWqJvrvs.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>38</v>
+        <v>598</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>피로 개선 효과 체감 — 복용 후 피로감이 덜한 것을 몸으로 체감함</t>
+          <t>소량 구매의 편의성 — 홈쇼핑 대량 구매와 달리 필요할 때 소량만 구매 가능함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>위생적인 소포장 형태 — 12포 소포장으로 깔끔하게 한 포씩 먹기 용이함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>뛰어난 가격과 구매성 — 가격이 합리적이며 매장에서 쉽게 구매 가능함</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>환절기 목 건강 관리 — 개별 포장되어 따뜻한 물에 타서 목 관리에 활용하기 좋음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>단맛 부족과 강한 쓴맛 — 단맛이 없고 생강 특유의 쓴맛이 강해 입에 맞지 않을 수 있음</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>잦은 제품 품절 — 원할 때 매장에서 품절되어 있는 경우가 자주 발생함</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -4818,22 +4797,22 @@
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>6978</v>
+        <v>6988</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 30일분을 저렴한 가격으로 꾸준히 복용하기 적합함</t>
+          <t>숙면 유도에 도움 — 먹고 나면 푹 잘 수 있어서 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>눈가 떨림 케어 도움 — 눈가 떨림 증상이 있을 때 부담 없이 챙겨 먹기 좋음</t>
+          <t>뛰어난 가성비 — 가격이 저렴하여 떨어질 때마다 다이소에서 구매하기 좋음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>미미한 즉각 체감 — 복용 후 체감되는 변화가 뚜렷하게 크지 않음</t>
+          <t>미미한 효과 체감 — 사람에 따라 효능을 직접 느끼기 어려울 수 있음</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -4842,7 +4821,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4850,12 +4829,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4865,36 +4844,40 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4269</v>
+        <v>3688</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>작은 캡슐의 편안한 목넘김 — 캡슐 크기가 아담하고 말랑하여 목 넘김이 매우 수월함</t>
+          <t>우수한 휴대성 — 포 형태로 되어 있어 드링크제보다 가볍고 여행이나 상비용으로 제격임</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>눈 피로 완화 및 관리 — 전자기기 사용으로 지친 눈의 피로를 관리하는 데 도움을 줌</t>
+          <t>속 불편함 완화 — 속이 안 좋을 때 하나씩 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 — 30일치 분량을 매우 저렴한 가격에 구매할 수 있음</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>저렴한 브랜드 약품 — 믿을 수 있는 브랜드의 제품을 싸게 구매함</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>아쉬운 맛 — 약 맛이 기호에 맞지 않을 수 있음</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -4909,58 +4892,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3961</v>
+        <v>309</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>다이어트 관리 지원 — 녹차카테킨 성분이 다이어트 및 체중 관리를 보조함</t>
+          <t>구취 제거 및 상쾌함 — 캡슐을 터뜨려 먹으면 입안이 시원하고 깔끔해짐</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>집중력 향상 체감 — 카페인 성분으로 아침 집중력을 높이는 데 효과를 느낌</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>부담 없는 가성비 — 저렴한 가격대로 꾸준히 재구매하여 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>양치 대용 간편성 — 양치하기 애매한 상황에서 손쉽게 입가심할 수 있음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 레몬민트 맛이 맛없게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4968,50 +4951,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1097</v>
+        <v>2659</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>재미있는 톡톡 식감 — 입안에서 톡톡 터지는 식감이 느껴져 맛과 재미를 동시에 선사함</t>
+          <t>어지럼증 완화 체감 — 함량이 좋고 복용 후 가끔 느끼던 어지러움이 개선됨</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>체중 유지 도움 — 체중 유지 및 관리를 지속하는 데 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>우수한 휴대성 — 한 포씩 챙기기 편하여 여행 시 지니고 다니기 적합함</t>
-        </is>
-      </c>
+          <t>저렴한 착한 가격 — 30일분을 저렴하게 구매해 꾸준히 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -5019,7 +4998,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5027,12 +5006,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5042,41 +5021,41 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000204&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251121/aHjoRwP9ejVVuu8M0Td4600000204_00_01aHjoRwP9ejVVuu8M0Td4.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>1506</v>
+        <v>2889</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>빠른 근육 경련 완화 — 액상 제형으로 흡수가 빨라 다리에 쥐가 날 때 빠르게 완화됨</t>
+          <t>배변 활동 도움 — 화장실을 잘 가도록 도와줌</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>피로 회복 도움 — 마신 후 피로감이 감소하는 유용한 체감을 제공함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>약국 대비 합리적 가격 — 약국에서 파는 마그네슘 샷 제품보다 저렴한 편임</t>
-        </is>
-      </c>
+          <t>심리적 안정감 제공 — 안 먹는 것보다 낫다는 생각으로 지속 복용하게 됨</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>다소 옅은 제형 농도 — 액상 농도가 아주 진하지는 않고 다소 묽은 편임</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>복용 후 졸음 및 피로 — 먹고 나면 심하게 잠이 오고 피곤해지는 현상이 발생함</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>불명확한 다이어트 효과 — 체중 감량 효과가 플라시보 수준이거나 장기 복용이 필요함</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5190,52 +5169,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -5247,52 +5226,48 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>홀베리</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>판티오</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
         </is>
       </c>
     </row>
@@ -5304,52 +5279,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 바나바잎 10정 10일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 셀레늄 아연 30정 30일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>홀베리 유기농 레몬생강즙 10포</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>동화 부채표 편안활 5포 5일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 철분 30정 30일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 밀크씨슬 6정 6일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[보령약국 X Pantio] [인교진 PICK] 60+ 에너지 올인원 12포 12일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 루테인 30정 30일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
         </is>
       </c>
     </row>
@@ -5360,13 +5335,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
@@ -5381,13 +5356,13 @@
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>4.7</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -5397,34 +5372,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2888</v>
+        <v>864</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2925</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>994</v>
+        <v>843</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>327</v>
+        <v>1952</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>38</v>
+        <v>598</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>6978</v>
+        <v>6988</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>4269</v>
+        <v>3688</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3961</v>
+        <v>309</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1097</v>
+        <v>2659</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1506</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -5435,66 +5410,63 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>원활한 배변 활동 도움 — 섭취 후 화장실을 쉽게 갈 수 있도록 도움을 줌</t>
+          <t>초저가 가성비 — 천원이라는 저렴한 가격으로 부담 없이 다이어트 및 건강 관리 가능함
+붓기 및 식곤증 완화 — 얼굴 붓기가 덜해지고 식후 졸음 현상이 줄어드는 느낌을 받음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>익숙한 일반 커피 맛 — 일반 커피와 유사한 맛으로 부담 없이 즐기기 좋음
-뛰어난 가성비 — 저렴한 가격으로 부담 없이 사서 챙겨 먹기 유용함</t>
+          <t>재구매 만족도 — 복용 후 개인적으로 효과를 보아 계속 쟁여두고 먹음
+간편한 영양 보충 — 필요한 아연과 셀레늄을 손쉽게 보충할 수 있음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>편리한 가루포 제형 — 사탕보다 먹기 편한 분말 형태라 간편하게 한 포씩 챙기기 좋음
-부담 없는 가성비 — 가격이 저렴하여 부담 없이 영양을 보충하기 좋음</t>
+          <t>운동 후 건강 관리 — 운동 후 섭취 시 체감 효과가 좋음
+제품 만족도 — 사용 후 만족스러워 재구매하여 꾸준히 복용함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 착한 가격 — 다이소 특유의 저렴한 가격으로 밀크씨슬을 챙길 수 있음
-간편한 휴대성 — 6정 소포장이라 여행이나 외출 시 간편히 지니기 좋음</t>
+          <t>저렴한 구매 가격 — 비싼 멀티비타민을 다이소에서 저렴하게 구매할 수 있음
+피로할 때 빠른 충전 — 피곤할 때 먹기 좋으며 맛도 무난함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>피로 개선 효과 체감 — 복용 후 피로감이 덜한 것을 몸으로 체감함
-위생적인 소포장 형태 — 12포 소포장으로 깔끔하게 한 포씩 먹기 용이함
-뛰어난 가격과 구매성 — 가격이 합리적이며 매장에서 쉽게 구매 가능함</t>
+          <t>소량 구매의 편의성 — 홈쇼핑 대량 구매와 달리 필요할 때 소량만 구매 가능함
+환절기 목 건강 관리 — 개별 포장되어 따뜻한 물에 타서 목 관리에 활용하기 좋음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 30일분을 저렴한 가격으로 꾸준히 복용하기 적합함
-눈가 떨림 케어 도움 — 눈가 떨림 증상이 있을 때 부담 없이 챙겨 먹기 좋음</t>
+          <t>숙면 유도에 도움 — 먹고 나면 푹 잘 수 있어서 좋음
+뛰어난 가성비 — 가격이 저렴하여 떨어질 때마다 다이소에서 구매하기 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>작은 캡슐의 편안한 목넘김 — 캡슐 크기가 아담하고 말랑하여 목 넘김이 매우 수월함
-눈 피로 완화 및 관리 — 전자기기 사용으로 지친 눈의 피로를 관리하는 데 도움을 줌
-부담 없는 가성비 — 30일치 분량을 매우 저렴한 가격에 구매할 수 있음</t>
+          <t>우수한 휴대성 — 포 형태로 되어 있어 드링크제보다 가볍고 여행이나 상비용으로 제격임
+속 불편함 완화 — 속이 안 좋을 때 하나씩 챙겨 먹기 편함
+저렴한 브랜드 약품 — 믿을 수 있는 브랜드의 제품을 싸게 구매함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>다이어트 관리 지원 — 녹차카테킨 성분이 다이어트 및 체중 관리를 보조함
-집중력 향상 체감 — 카페인 성분으로 아침 집중력을 높이는 데 효과를 느낌
-부담 없는 가성비 — 저렴한 가격대로 꾸준히 재구매하여 먹기 좋음</t>
+          <t>구취 제거 및 상쾌함 — 캡슐을 터뜨려 먹으면 입안이 시원하고 깔끔해짐
+양치 대용 간편성 — 양치하기 애매한 상황에서 손쉽게 입가심할 수 있음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>재미있는 톡톡 식감 — 입안에서 톡톡 터지는 식감이 느껴져 맛과 재미를 동시에 선사함
-체중 유지 도움 — 체중 유지 및 관리를 지속하는 데 도움을 줌
-우수한 휴대성 — 한 포씩 챙기기 편하여 여행 시 지니고 다니기 적합함</t>
+          <t>어지럼증 완화 체감 — 함량이 좋고 복용 후 가끔 느끼던 어지러움이 개선됨
+저렴한 착한 가격 — 30일분을 저렴하게 구매해 꾸준히 먹기 좋음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>빠른 근육 경련 완화 — 액상 제형으로 흡수가 빨라 다리에 쥐가 날 때 빠르게 완화됨
-피로 회복 도움 — 마신 후 피로감이 감소하는 유용한 체감을 제공함
-약국 대비 합리적 가격 — 약국에서 파는 마그네슘 샷 제품보다 저렴한 편임</t>
+          <t>배변 활동 도움 — 화장실을 잘 가도록 도와줌
+심리적 안정감 제공 — 안 먹는 것보다 낫다는 생각으로 지속 복용하게 됨</t>
         </is>
       </c>
     </row>
@@ -5506,34 +5478,38 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>졸음 및 피로감 유발 — 섭취 후 졸음이 심하게 오거나 피로감이 느껴지는 현상이 있음
-미미한 체감 효과 — 체중 감량이나 신체 변화 등의 효과가 명확히 느껴지지 않음</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>은은한 한방 향 감돌음 — 커피 맛 뒤에 약간의 한방 향이 느껴져 호불호가 갈림
-적은 분량의 용량 — 한 상자에 5일분만 들어있어 금방 소진되는 점이 아쉬움</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>강한 단맛과 사탕 느낌 — 단맛이 강해 비타민 영양제보다는 레몬사탕에 가깝게 느껴짐</t>
-        </is>
-      </c>
+          <t>체감 효과 미비 — 눈에 띄는 다이어트 체감 효과는 명확하지 않음</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>단맛 부족과 강한 쓴맛 — 단맛이 없고 생강 특유의 쓴맛이 강해 입에 맞지 않을 수 있음
+잦은 제품 품절 — 원할 때 매장에서 품절되어 있는 경우가 자주 발생함</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>미미한 즉각 체감 — 복용 후 체감되는 변화가 뚜렷하게 크지 않음</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+          <t>미미한 효과 체감 — 사람에 따라 효능을 직접 느끼기 어려울 수 있음</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>아쉬운 맛 — 약 맛이 기호에 맞지 않을 수 있음</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 레몬민트 맛이 맛없게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>다소 옅은 제형 농도 — 액상 농도가 아주 진하지는 않고 다소 묽은 편임</t>
+          <t>복용 후 졸음 및 피로 — 먹고 나면 심하게 잠이 오고 피곤해지는 현상이 발생함
+불명확한 다이어트 효과 — 체중 감량 효과가 플라시보 수준이거나 장기 복용이 필요함</t>
         </is>
       </c>
     </row>
@@ -5545,22 +5521,22 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -5580,12 +5556,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5678,7 +5654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5715,16 +5691,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -5734,16 +5710,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>23.3</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -5768,26 +5744,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5797,16 +5773,16 @@
         <v>3.3</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5825,7 +5801,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5838,44 +5814,6 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
         <v>0</v>
       </c>
     </row>
